--- a/data/players.xlsx
+++ b/data/players.xlsx
@@ -1,40 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chua Shi Min\Documents\world_cup\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8D2148A-D5CA-44AB-9C49-50AFBD89AF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BAED2D-F780-4A9F-8494-1E7BE604D348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5340" yWindow="-21720" windowWidth="38640" windowHeight="21240" activeTab="5" xr2:uid="{2BC7C48E-01B7-4D36-AC99-3F24307DB5A1}"/>
+    <workbookView xWindow="-5340" yWindow="-21720" windowWidth="38640" windowHeight="21240" activeTab="2" xr2:uid="{2BC7C48E-01B7-4D36-AC99-3F24307DB5A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
     <sheet name="pivot" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet7" sheetId="9" r:id="rId4"/>
-    <sheet name="federation" sheetId="5" r:id="rId5"/>
-    <sheet name="players" sheetId="1" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet7" sheetId="9" r:id="rId5"/>
+    <sheet name="federation" sheetId="5" r:id="rId6"/>
+    <sheet name="players" sheetId="1" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">federation!$A$1:$D$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">federation!$A$1:$D$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$1:$C$50</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId7"/>
-    <pivotCache cacheId="4" r:id="rId8"/>
-    <pivotCache cacheId="5" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId10"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7841" uniqueCount="2952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7941" uniqueCount="2952">
   <si>
     <t>player</t>
   </si>
@@ -27916,7 +27917,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1168D2C6-BB66-48F0-8E9F-0C6ED1E0D21D}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1168D2C6-BB66-48F0-8E9F-0C6ED1E0D21D}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B77" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -29515,7 +29516,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1EA2EF3-C25D-41F3-A1CE-81310B26A325}" name="PivotTable4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1EA2EF3-C25D-41F3-A1CE-81310B26A325}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="2">
     <pivotField showAll="0"/>
@@ -29534,7 +29535,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD9237A9-0DD4-4A00-961C-369CD2349415}" name="PivotTable6" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD9237A9-0DD4-4A00-961C-369CD2349415}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" showAll="0"/>
@@ -30745,6 +30746,575 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21E2AA5-C361-4005-82C9-A89EB01BB0A5}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2931</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>2929</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>870</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>937</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>736</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>720</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>2877</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2930</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2923</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2926</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2924</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>2488</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>2927</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C50" xr:uid="{B21E2AA5-C361-4005-82C9-A89EB01BB0A5}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="UEFA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87F6123-9170-4564-9FEA-E94ADEEC63EF}">
   <dimension ref="A3:C20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -30844,7 +31414,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D71D7303-D5AB-4C2B-B236-02C68AD97AEC}">
   <dimension ref="A3:F14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -31015,7 +31585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E28CFF6-5A30-4BC4-BE7D-72D1CF85D3D4}">
   <dimension ref="A1:E73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -31893,7 +32463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC1108F-9CC4-434E-9BCF-6AEDD3C166BD}">
   <dimension ref="A1:K1249"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
